--- a/output/pdf_financials_xlsx/IMO.xlsx
+++ b/output/pdf_financials_xlsx/IMO.xlsx
@@ -601,35 +601,23 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -723,35 +711,23 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -778,35 +754,23 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -833,35 +797,23 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
@@ -888,53 +840,41 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>31945</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>24965</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>24910</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>28842</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>32026</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>32055</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>24796</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>34307</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>50186</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>45293</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>42816</v>
       </c>
     </row>
     <row r="11">
@@ -1010,35 +950,23 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1065,35 +993,23 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
@@ -1120,35 +1036,23 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -1175,35 +1079,23 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>22492</v>
@@ -1285,35 +1177,23 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>551</v>
@@ -1529,35 +1409,23 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -1584,35 +1452,23 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -16790,7 +16646,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -18116,7 +17972,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
